--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104584_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104584_W14.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0752</v>
+        <v>8.851100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.091</v>
+        <v>3.6475</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9842</v>
+        <v>5.2035</v>
       </c>
       <c r="G2" t="n">
-        <v>3.419</v>
+        <v>3.4132</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5527</v>
+        <v>2.5478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8663</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1016</v>
+        <v>2.0757</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8458</v>
+        <v>1.8304</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3174</v>
+        <v>1.3375</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>4.083</v>
+        <v>4.0974</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6828</v>
+        <v>0.4575</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8702</v>
+        <v>1.4628</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1874</v>
+        <v>-1.0053</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.786</v>
+        <v>3.3763</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9766</v>
+        <v>4.8154</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1906</v>
+        <v>-1.4392</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3975</v>
+        <v>5.3773</v>
       </c>
       <c r="H3" t="n">
-        <v>5.664</v>
+        <v>5.6392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2665</v>
+        <v>-0.262</v>
       </c>
       <c r="J3" t="n">
-        <v>6.3164</v>
+        <v>6.2768</v>
       </c>
       <c r="K3" t="n">
-        <v>5.7594</v>
+        <v>5.7259</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.8995</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7346</v>
+        <v>0.3357</v>
       </c>
       <c r="T3" t="n">
-        <v>0.248</v>
+        <v>0.1321</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4866</v>
+        <v>0.2036</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9275</v>
+        <v>3.0748</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1219</v>
+        <v>3.8662</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0494</v>
+        <v>-0.7915</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2548</v>
+        <v>0.7439</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2223</v>
+        <v>-1.3207</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4771</v>
+        <v>2.0647</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6845</v>
+        <v>2.2302</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3432</v>
+        <v>-1.0762</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3413</v>
+        <v>3.3064</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4297</v>
+        <v>-1.4863</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5655</v>
+        <v>-0.2446</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1359</v>
+        <v>-1.2417</v>
       </c>
       <c r="P4" t="n">
-        <v>2.722</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4603</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5626</v>
+        <v>0.2993</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1023</v>
+        <v>-0.2157</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.781</v>
+        <v>2.482</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7827</v>
+        <v>0.0974</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0017</v>
+        <v>2.3847</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7502</v>
+        <v>-0.2566</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.313</v>
+        <v>0.2185</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0631</v>
+        <v>-0.4751</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2582</v>
+        <v>-0.7059</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0603</v>
+        <v>-0.3555</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3185</v>
+        <v>-0.3505</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.508</v>
+        <v>0.4493</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2526</v>
+        <v>0.574</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2554</v>
+        <v>-0.1246</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>2.7316</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2226</v>
+        <v>0.0071</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1785</v>
+        <v>0.8033</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4011</v>
+        <v>-0.7962</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1865</v>
+        <v>2.3231</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2103</v>
+        <v>2.1969</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0238</v>
+        <v>0.1263</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1874</v>
+        <v>1.1875</v>
       </c>
       <c r="H6" t="n">
         <v>0.3131</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8743</v>
+        <v>0.8744</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8746</v>
+        <v>1.8581</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2353</v>
+        <v>0.2273</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6871</v>
+        <v>-0.6706</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.277</v>
+        <v>0.4041</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3357</v>
+        <v>0.3388</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0587</v>
+        <v>0.0653</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5322</v>
+        <v>1.6582</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2599</v>
+        <v>2.3271</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7277</v>
+        <v>-0.6688</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1568</v>
+        <v>1.1244</v>
       </c>
       <c r="H7" t="n">
-        <v>2.367</v>
+        <v>2.3339</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2101</v>
+        <v>-1.2095</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3744</v>
+        <v>2.3253</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6037</v>
+        <v>2.5641</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2176</v>
+        <v>-1.2009</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4927</v>
+        <v>0.6445</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1785</v>
+        <v>0.2993</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3142</v>
+        <v>0.3452</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0172</v>
+        <v>1.3588</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6881</v>
+        <v>-0.3606</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7053</v>
+        <v>1.7194</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4983</v>
+        <v>-0.3381</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4692</v>
+        <v>-0.41</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9675</v>
+        <v>0.0718</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6448</v>
+        <v>-1.2612</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5328000000000001</v>
+        <v>-1.1419</v>
       </c>
       <c r="L8" t="n">
-        <v>0.112</v>
+        <v>-0.1194</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1431</v>
+        <v>0.9231</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0636</v>
+        <v>0.7319</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0795</v>
+        <v>0.1912</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>2.9592</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1757</v>
+        <v>2.9592</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2867</v>
+        <v>-0.5598</v>
       </c>
       <c r="T8" t="n">
-        <v>0.614</v>
+        <v>0.7428</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3273</v>
+        <v>-1.3027</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3214</v>
+        <v>-0.7025</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3214</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7294</v>
+        <v>1.1866</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9885</v>
+        <v>-0.6034</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2591</v>
+        <v>1.79</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.144</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6291</v>
+        <v>0.4519</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4851</v>
+        <v>-0.9605</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.435</v>
+        <v>0.6213</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.88</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4451</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>0.291</v>
+        <v>-1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.251</v>
+        <v>-0.0578</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04</v>
+        <v>-1.0722</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>3.1868</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5123</v>
+        <v>0.4692</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1039</v>
+        <v>0.736</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5916</v>
+        <v>-0.2669</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5463</v>
+        <v>0.3155</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5463</v>
+        <v>0.3155</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0945</v>
+        <v>0.0926</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.279</v>
+        <v>0.1472</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3735</v>
+        <v>-0.0546</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3326</v>
+        <v>-0.1476</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3966</v>
+        <v>-0.6317</v>
       </c>
       <c r="I10" t="n">
-        <v>0.064</v>
+        <v>0.4841</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.234</v>
+        <v>-0.4506</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1194</v>
+        <v>-0.8898</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1147</v>
+        <v>0.4392</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9015</v>
+        <v>0.303</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7228</v>
+        <v>0.2581</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1787</v>
+        <v>0.0449</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9488</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9488</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8147</v>
+        <v>-0.1255</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2056</v>
+        <v>0.2808</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.609</v>
+        <v>-0.4063</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7071</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.405</v>
+        <v>-0.2491</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7337</v>
+        <v>0.0075</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3288</v>
+        <v>-0.2566</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3386</v>
+        <v>2.3719</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4718</v>
+        <v>1.7582</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8104</v>
+        <v>0.6138</v>
       </c>
       <c r="J11" t="n">
-        <v>0.578</v>
+        <v>1.8661</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.09370000000000001</v>
+        <v>1.658</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6717</v>
+        <v>0.2081</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2395</v>
+        <v>0.5058</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3781</v>
+        <v>0.1002</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1387</v>
+        <v>0.4057</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8562</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4606</v>
+        <v>0.1498</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5444</v>
+        <v>0.6454</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0838</v>
+        <v>-0.4956</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6105</v>
+        <v>-1.405</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6105</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6392</v>
+        <v>-0.4939</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1988</v>
+        <v>-2.7518</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4404</v>
+        <v>2.2578</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3794</v>
+        <v>0.3428</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7663</v>
+        <v>-0.4738</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6131</v>
+        <v>0.8166</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8911</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6726</v>
+        <v>-0.1002</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2185</v>
+        <v>0.6703</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4883</v>
+        <v>-0.2273</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.3736</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3946</v>
+        <v>0.1463</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.361</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-3.8697</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2435</v>
+        <v>0.3681</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4053</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6488</v>
+        <v>-0.1797</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4141</v>
+        <v>0.6162</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4141</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8544</v>
+        <v>-2.451</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.803</v>
+        <v>-4.2333</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9486</v>
+        <v>1.7823</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0937</v>
+        <v>-2.0936</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3476</v>
+        <v>1.3552</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.4413</v>
+        <v>-3.4488</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.4269</v>
+        <v>-3.4456</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4676</v>
+        <v>0.4654</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.8945</v>
+        <v>-3.911</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3333</v>
+        <v>1.352</v>
       </c>
       <c r="N13" t="n">
-        <v>0.88</v>
+        <v>0.8898</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0537</v>
+        <v>-0.6549</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2419</v>
+        <v>0.3505</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8118</v>
+        <v>-1.0053</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.2309</v>
+        <v>21.20950000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>9.484500000000004</v>
+        <v>9.156100000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>11.7465</v>
+        <v>12.0533</v>
       </c>
       <c r="G14" t="n">
-        <v>11.3055</v>
+        <v>11.2165</v>
       </c>
       <c r="H14" t="n">
-        <v>11.8917</v>
+        <v>11.7816</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5862000000000007</v>
+        <v>-0.5650999999999997</v>
       </c>
       <c r="J14" t="n">
-        <v>12.2587</v>
+        <v>11.9603</v>
       </c>
       <c r="K14" t="n">
-        <v>9.6206</v>
+        <v>9.417100000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>2.638</v>
+        <v>2.543</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9530000000000003</v>
+        <v>-0.7439000000000002</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2712</v>
+        <v>2.3644</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.2244</v>
+        <v>-3.1081</v>
       </c>
       <c r="P14" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.6101</v>
+        <v>-13.6579</v>
       </c>
       <c r="R14" t="n">
-        <v>24.9517</v>
+        <v>25.0396</v>
       </c>
       <c r="S14" t="n">
-        <v>1.572499999999999</v>
+        <v>1.5794</v>
       </c>
       <c r="T14" t="n">
-        <v>6.593599999999999</v>
+        <v>6.639000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.021000000000001</v>
+        <v>-5.059600000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.989099999999999</v>
+        <v>-2.9677</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2422</v>
+        <v>4.215</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.231400000000001</v>
+        <v>-7.1829</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3298</v>
+        <v>3.8031</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8552</v>
+        <v>3.4828</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5254</v>
+        <v>0.3203</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6568</v>
+        <v>1.6672</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6381</v>
+        <v>-0.6158</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2949</v>
+        <v>2.2831</v>
       </c>
       <c r="J15" t="n">
-        <v>1.887</v>
+        <v>1.8678</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7831</v>
+        <v>1.7644</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2302</v>
+        <v>-0.2006</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.742</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5538</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2612</v>
+        <v>0.9125</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.815</v>
+        <v>-1.0042</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2242</v>
+        <v>1.4848</v>
       </c>
       <c r="E16" t="n">
-        <v>3.296</v>
+        <v>2.8053</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0718</v>
+        <v>-1.3205</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5193</v>
+        <v>0.537</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6606</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1413</v>
+        <v>-0.14</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4373</v>
+        <v>1.4258</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4027</v>
+        <v>1.3962</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0346</v>
+        <v>0.0296</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9179</v>
+        <v>-0.8888</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.742</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.839</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8075</v>
+        <v>0.3388</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0314</v>
+        <v>-0.2527</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9263</v>
+        <v>1.1781</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1045</v>
+        <v>0.0135</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0308</v>
+        <v>1.1645</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7733</v>
+        <v>0.7808</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7733</v>
+        <v>0.7808</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7387</v>
+        <v>0.7463</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7387</v>
+        <v>0.7463</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5275</v>
+        <v>-0.2856</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3883</v>
+        <v>-0.2647</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1754</v>
+        <v>-0.3859</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3978</v>
+        <v>0.7448</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2224</v>
+        <v>-1.1307</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5278</v>
+        <v>1.9542</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6234</v>
+        <v>2.4896</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0956</v>
+        <v>-0.5353</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4088</v>
+        <v>3.8299</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5208</v>
+        <v>2.7062</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>1.1237</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1189</v>
+        <v>-1.8756</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1026</v>
+        <v>-0.2166</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9837</v>
+        <v>-1.659</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7814</v>
+        <v>-0.3809</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1867</v>
+        <v>0.2203</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4053</v>
+        <v>-0.6012</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.743</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7624</v>
+        <v>-0.3549</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6238</v>
+        <v>-0.3881</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3429</v>
+        <v>1.5836</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0448</v>
+        <v>0.4216</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2981</v>
+        <v>1.162</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07199999999999999</v>
+        <v>3.3302</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0346</v>
+        <v>1.1409</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>2.1893</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4149</v>
+        <v>-1.7466</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0795</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3354</v>
+        <v>-1.0273</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0402</v>
+        <v>0.1985</v>
       </c>
       <c r="T19" t="n">
-        <v>0.369</v>
+        <v>0.3456</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4092</v>
+        <v>-0.1471</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3856</v>
+        <v>-0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>-0.6162</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7071</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1049</v>
+        <v>-0.7533</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2012</v>
+        <v>-1.4719</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9038</v>
+        <v>0.7186</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5706</v>
+        <v>-1.5154</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4111</v>
+        <v>-2.6195</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1595</v>
+        <v>1.1042</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3521</v>
+        <v>-1.4159</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1531</v>
+        <v>-1.5276</v>
       </c>
       <c r="L20" t="n">
-        <v>2.199</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7815</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.742</v>
+        <v>-1.092</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0395</v>
+        <v>0.9925</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5878</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1558</v>
+        <v>1.1962</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4597</v>
+        <v>1.1308</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6155</v>
+        <v>0.0653</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6105</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3214</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5803</v>
+        <v>-0.833</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6082</v>
+        <v>0.5218</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9722</v>
+        <v>-1.3547</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7751</v>
+        <v>-1.332</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4213</v>
+        <v>-0.0377</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1964</v>
+        <v>-1.2943</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0698</v>
+        <v>0.0717</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8312</v>
+        <v>0.0345</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.901</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7053</v>
+        <v>-1.4037</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4099</v>
+        <v>-0.0722</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2954</v>
+        <v>-1.3315</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4216</v>
+        <v>-0.0245</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5958</v>
+        <v>0.1345</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1742</v>
+        <v>-0.159</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0132</v>
+        <v>-1.3852</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0264</v>
+        <v>-0.6208</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9868</v>
+        <v>-0.7645</v>
       </c>
       <c r="G22" t="n">
-        <v>1.9577</v>
+        <v>-1.7708</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4803</v>
+        <v>0.4249</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5225</v>
+        <v>-2.1957</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8647</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7187</v>
+        <v>0.8274</v>
       </c>
       <c r="L22" t="n">
-        <v>1.146</v>
+        <v>-0.909</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.907</v>
+        <v>-1.6891</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2384</v>
+        <v>-0.4025</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6685</v>
+        <v>-1.2866</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0221</v>
+        <v>0.6132</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6079</v>
+        <v>0.5991</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4142</v>
+        <v>0.0141</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2758</v>
+        <v>-2.1641</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7655</v>
+        <v>-2.5004</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5103</v>
+        <v>0.3363</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4107</v>
+        <v>-1.4045</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8715</v>
+        <v>-2.872</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4608</v>
+        <v>1.4676</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.866</v>
+        <v>-0.888</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.714</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5447</v>
+        <v>-0.5164</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.1575</v>
+        <v>-2.1406</v>
       </c>
       <c r="O23" t="n">
-        <v>1.6127</v>
+        <v>1.6242</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6895</v>
+        <v>0.4272</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5898</v>
+        <v>0.7126</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0997</v>
+        <v>-0.2854</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.378</v>
+        <v>-4.2459</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5743</v>
+        <v>-3.3837</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8037</v>
+        <v>-0.8622</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.928</v>
+        <v>-2.9256</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.6263</v>
+        <v>-3.6165</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6983</v>
+        <v>0.6909</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1465</v>
+        <v>-1.1791</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.0415</v>
+        <v>-3.0551</v>
       </c>
       <c r="L24" t="n">
-        <v>1.895</v>
+        <v>1.8761</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7815</v>
+        <v>-1.7466</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5848</v>
+        <v>-0.5613</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0475</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1179</v>
+        <v>0.1204</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0704</v>
+        <v>-0.0262</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3493</v>
+        <v>-5.8706</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.633</v>
+        <v>-5.4413</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7163</v>
+        <v>-0.4293</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.2484</v>
+        <v>-5.2489</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.2163</v>
+        <v>-5.213</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.032</v>
+        <v>-0.0359</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.3414</v>
+        <v>-4.3733</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.3257</v>
+        <v>-3.3449</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.0157</v>
+        <v>-1.0284</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.907</v>
+        <v>-0.8756</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.8906</v>
+        <v>-1.8681</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0614</v>
+        <v>0.4286</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1089</v>
+        <v>0.348</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1703</v>
+        <v>0.0805</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W25" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.9728</v>
+        <v>-7.3463</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.3492</v>
+        <v>-5.8486</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6236</v>
+        <v>-1.4977</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.5504</v>
+        <v>-3.542</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.6178</v>
+        <v>-1.6007</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.9326</v>
+        <v>-1.9414</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.862</v>
+        <v>-1.878</v>
       </c>
       <c r="K26" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.914</v>
+        <v>-1.9298</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.6884</v>
+        <v>-1.664</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.6698</v>
+        <v>-1.6524</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R26" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S26" t="n">
-        <v>0.483</v>
+        <v>0.1078</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6866</v>
+        <v>0.2179</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2036</v>
+        <v>-0.11</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-21.2308</v>
+        <v>-17.2613</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.7465</v>
+        <v>-12.0534</v>
       </c>
       <c r="F27" t="n">
-        <v>-9.484500000000001</v>
+        <v>-5.208</v>
       </c>
       <c r="G27" t="n">
-        <v>-11.3056</v>
+        <v>-11.2164</v>
       </c>
       <c r="H27" t="n">
-        <v>-11.8916</v>
+        <v>-11.7814</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5652000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9532000000000007</v>
+        <v>0.7439000000000002</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.271199999999999</v>
+        <v>-2.3642</v>
       </c>
       <c r="L27" t="n">
-        <v>3.2243</v>
+        <v>3.1082</v>
       </c>
       <c r="M27" t="n">
-        <v>-12.2586</v>
+        <v>-11.9602</v>
       </c>
       <c r="N27" t="n">
-        <v>-9.6204</v>
+        <v>-9.417300000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.638100000000001</v>
+        <v>-2.5428</v>
       </c>
       <c r="P27" t="n">
-        <v>-11.3416</v>
+        <v>-11.3814</v>
       </c>
       <c r="Q27" t="n">
-        <v>-24.9517</v>
+        <v>-25.0396</v>
       </c>
       <c r="R27" t="n">
-        <v>13.6099</v>
+        <v>13.6579</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.5728</v>
+        <v>2.3689</v>
       </c>
       <c r="T27" t="n">
-        <v>5.020700000000001</v>
+        <v>5.0595</v>
       </c>
       <c r="U27" t="n">
-        <v>-6.593500000000001</v>
+        <v>-2.6906</v>
       </c>
       <c r="V27" t="n">
-        <v>2.988999999999999</v>
+        <v>2.9678</v>
       </c>
       <c r="W27" t="n">
-        <v>7.231399999999999</v>
+        <v>7.1828</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.2424</v>
+        <v>-4.215</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104584_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104584_W14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.1829</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104584_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-4.215</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
